--- a/cat_dua/upload/temp/SMA.xlsx
+++ b/cat_dua/upload/temp/SMA.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Documents\SOAL UJIAN CAT\TPA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Documents\CAT SOAL UJIAN\TPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B0CB9D-3331-4D2A-9F99-D3613D0892F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -748,10 +747,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;Rp&quot;#,##0.00;[Red]\-&quot;Rp&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="8" formatCode="&quot;Rp&quot;#,##0.00;[Red]\-&quot;Rp&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -883,7 +882,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -922,7 +921,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1018,23 +1017,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1070,23 +1052,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1262,14 +1227,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P107"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="5" customWidth="1"/>
     <col min="2" max="2" width="56" style="6" customWidth="1"/>
     <col min="3" max="6" width="22.140625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="34.7109375" style="5" customWidth="1"/>
     <col min="9" max="16" width="0" hidden="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" hidden="1"/>
@@ -2602,8 +2567,8 @@
     <row r="106" x14ac:dyDescent="0.25"/>
     <row r="107" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H92" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H92">
       <formula1>$K$1:$O$1</formula1>
     </dataValidation>
   </dataValidations>
